--- a/reports/20260507/Sprint_217_AO.xlsx
+++ b/reports/20260507/Sprint_217_AO.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,12 +36,8 @@
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -94,9 +84,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,7 +686,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,17 +694,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** *** C A N D I D A T E - C R E A T E D ***  ===&gt;  true (PASS), *** C A N D I D A T E - I d ***  ===&gt; 1607441 (PASS)</t>
         </is>
       </c>
     </row>
@@ -758,15 +743,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'candidateId')</t>
+Assertions: ***C A N D I D A T E - I D  -  V E R I F I C A T I O N ***  ==&gt;  1607441 (PASS)</t>
         </is>
       </c>
     </row>
@@ -799,7 +784,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -807,17 +792,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: ***C A N D I D A T E - I D  -  V E R I F I C A T I O N ***  ==&gt;  1607441 (PASS), ***C A N D I D A T E - U P D A T E  -  V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -850,7 +833,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -858,17 +841,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: ***C A N D I D A T E - I D  -  V E R I F I C A T I O N ***  ==&gt;  1607441 (PASS), ***C A N D I D A T E - U P D A T E  -  V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -901,7 +882,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -909,17 +890,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: ***C A N D I D A T E - I D  -  V E R I F I C A T I O N ***  ==&gt;  1607441 (PASS)</t>
         </is>
       </c>
     </row>
@@ -960,15 +939,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'faceMatchPercentage')</t>
+Assertions: *** F A C E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  0 (PASS), *** F A C E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  No Match (PASS), *** F A C E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -1009,15 +988,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'faceMatched')</t>
+Assertions: *** F A C E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  No Match (PASS), *** F A C E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1044,8 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 200 - OK</t>
+          <t>Response Code: 200 - OK
+Assertions: *** I N T E R V I E W - I D ***  ==&gt;  65803 (PASS), *** I N T E R V I E W - L I N K ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1093,8 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 200 - OK</t>
+          <t>Response Code: 200 - OK
+Assertions: *** I N T E R V I E W - I D ***  ==&gt;  65805 (PASS), *** L I N K S - A R E - N O T - M A T C H E D - V E R I F I E D ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1143,7 @@
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** I N T E R V I E W - F A I L E D - D E T A I L S ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** I N T E R V I E W - D E T A I L S ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -1203,15 +1184,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'candidateId')</t>
+Assertions: ***C A N D I D A T E - ID  -  V E R I F I C A T I O N ***  ==&gt;  1607441 (PASS)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1241,7 @@
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** M A R K - I N T E R V I E W - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** M A R K - I N T E R V I E W - C O M P L E T E D ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1290,7 @@
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** C A N C E L L E D - I N T E R V I E W  - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** C A N C E L L E D - I N T E R V I E W - I D ***  ==&gt;  65805 (PASS)</t>
         </is>
       </c>
     </row>
@@ -1496,15 +1477,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'interviewerLinks')</t>
+Assertions: *** I N T E R V I E W - I D ***  ==&gt;  65807 (PASS), *** I N T E R V I E W - L I N K ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1534,7 @@
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** C A N C E L L E D - I N T E R V I E W  - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** C A N C E L L E D - I N T E R V I E W - I D ***  ==&gt;  65807 (PASS)</t>
         </is>
       </c>
     </row>
@@ -1594,16 +1575,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** I N T E R V I E W - S C H E D U L E - F A I L U R E ***  ==&gt;  Invalid input.  time should not be older than 48 hours from current date-time. (PASS)
-Errors: Cannot read properties of undefined (reading 'interviewerLinks')</t>
+Assertions: *** I N T E R V I E W - S C H E D U L E - F A I L U R E ***  ==&gt;  Invalid input.  time should not be older than 48 hours from current date-time. (PASS)</t>
         </is>
       </c>
     </row>
@@ -1693,15 +1673,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Errors: Cannot read properties of undefined (reading 'interviewerLinks')</t>
+Assertions: *** I N T E R V I E W - I D ***  ==&gt;  65809 (PASS), *** I N T E R V I E W - L I N K ***  ==&gt;   (PASS)</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1730,7 @@
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Response Code: 200 - OK
-Assertions: *** C A N C E L L E D - I N T E R V I E W  - F A I L E D ***  ==&gt;  Invalid input.  not found. (PASS)</t>
+Assertions: *** C A N C E L L E D - I N T E R V I E W - I D ***  ==&gt;  65809 (PASS)</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1910,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1938,17 +1918,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** N O - F A C E - V E R I F I C A T I O N ***  ==&gt;  No face detected. (PASS)</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1959,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1989,17 +1967,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** N O T - V A L I D - P H O T O - V E R I F I C A T I O N ***  ==&gt;  Not a valid photo. (PASS)</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2008,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2040,17 +2016,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** M O R E - F A C E S - V E R I F I C A T I O N ***  ==&gt;  More than one face detected. (PASS)</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2057,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2091,17 +2065,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** N O - F A C E - V E R I F I C A T I O N ***  ==&gt;  No face detected. (PASS)</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2106,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2142,17 +2114,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** M O R E - F A C E S - V E R I F I C A T I O N ***  ==&gt;  More than one face detected. (PASS)</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2155,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2193,17 +2163,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** M O R E - F A C E - V E R I F I C A T I O N ***  ==&gt;  Only one face detected. (PASS)</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2204,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2244,17 +2212,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** P A S S P O R T - N A M E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  Full (PASS), *** P A S S P O R T - I D - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2253,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2295,17 +2261,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** A A D H A A R - N A M E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  Full (PASS), *** A A D H A A R - I D - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2302,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2346,17 +2310,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** P A N - N A M E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  Full (PASS), *** P A N - I D - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2351,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2397,17 +2359,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** N A M E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  No (PASS), *** I D - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2400,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Status Code: 403 - Forbidden and all assertions should pass.</t>
+          <t>Status Code: 200 - OK and all assertions should pass.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2448,17 +2408,15 @@
           <t>All assertions pass.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Response Code: 403 - Forbidden
-Errors: Unexpected token '&lt;' at 1:1
-&lt;html&gt;
-^</t>
+          <t>Response Code: 200 - OK
+Assertions: *** N A M E - M A T C H - V E R I F I C A T I O N ***  ==&gt;  Partial (PASS), *** I D - M A T C H - V E R I F I C A T I O N ***  ==&gt;  true (PASS)</t>
         </is>
       </c>
     </row>
